--- a/reports/nifty100_daily_report_20260420.xlsx
+++ b/reports/nifty100_daily_report_20260420.xlsx
@@ -9537,7 +9537,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Signal Tracker  |  Total: 34  |  Active: 34  |  Profitable: 0/34  |  Avg Ret: +0.00%  |  Best: ADANIPORTS (+0.0%)  |  As of: 2026-04-20</t>
+          <t>Signal Tracker  |  Total: 34  |  Active: 34  |  Profitable: 0/34  |  Avg Ret: +0.00%  |  Best: ADANIPORTS (+0.0%)  |  As of: 2026-04-19</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="W3" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X3" s="14" t="n">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="W4" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X4" s="14" t="n">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="W5" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X5" s="14" t="n">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="W6" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X6" s="14" t="n">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="W7" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X7" s="14" t="n">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="W8" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X8" s="14" t="n">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="W9" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X9" s="14" t="n">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="W10" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X10" s="14" t="n">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="W11" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X11" s="14" t="n">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="W12" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X12" s="14" t="n">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="W13" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X13" s="14" t="n">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="W14" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X14" s="14" t="n">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="W15" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X15" s="14" t="n">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="W16" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X16" s="14" t="n">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="W17" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X17" s="14" t="n">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="W18" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X18" s="14" t="n">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="W19" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X19" s="14" t="n">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="W20" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X20" s="14" t="n">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="W21" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X21" s="14" t="n">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="W22" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X22" s="14" t="n">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="W23" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X23" s="14" t="n">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="W24" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X24" s="14" t="n">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="W25" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X25" s="14" t="n">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="W26" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X26" s="14" t="n">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="W27" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X27" s="14" t="n">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="W28" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X28" s="14" t="n">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="W29" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X29" s="14" t="n">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="W30" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X30" s="14" t="n">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="W31" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X31" s="14" t="n">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="W32" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X32" s="14" t="n">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="W33" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X33" s="14" t="n">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="W34" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X34" s="14" t="n">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="W35" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X35" s="14" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="W36" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="X36" s="14" t="n">
